--- a/data/kocaeli/km_data.xlsx
+++ b/data/kocaeli/km_data.xlsx
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>60833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>48044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>81154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>81551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>69737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>33747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>33259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:49</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>27646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:50</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>23240</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-26 16:43:50</t>
+          <t>2026-03-05 19:23:45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>bootstrap</t>
+          <t>mciftci</t>
         </is>
       </c>
     </row>
